--- a/templates/03_Room_Process_Master.xlsx
+++ b/templates/03_Room_Process_Master.xlsx
@@ -425,20 +425,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,12 +501,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ROOM-A</t>
+          <t>ROOM-G</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FILL-HI</t>
+          <t>FILL-NEW</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -520,34 +520,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>8</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>High-speed filling</t>
+          <t>New filling room</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ROOM-A</t>
+          <t>ROOM-G</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FILL-STD</t>
+          <t>PACK-NEW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,350 +557,61 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TYPE-A</t>
+          <t>TYPE-B</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Standard filling</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROOM-B</t>
+          <t>ROOM-H</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FILL-STD</t>
+          <t>AUTO-SEAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TYPE-A</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>55</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>TYPE-C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Filling room B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ROOM-C</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PACK-BULK</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TYPE-B</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Bulk packing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ROOM-C</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PACK-STD</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TYPE-B</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>45</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Standard packing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ROOM-D</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PACK-STD</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TYPE-B</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Packing room D</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ROOM-E</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LABEL-AUTO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TYPE-C</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>500</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Auto labeler</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ROOM-E</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SEAL-AUTO</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TYPE-C</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>350</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
           <t>Auto sealer</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ROOM-F</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SEMI-MIX</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TYPE-D</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>35</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Semi-fin mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ROOM-F</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SEMI-PROC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TYPE-D</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Semi-fin proc</t>
         </is>
       </c>
     </row>
